--- a/9. Statement and Data Notes.xlsx
+++ b/9. Statement and Data Notes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BD0665D-2C06-2642-886C-836527163976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E69D214F-627C-2646-A4EE-B2266F272715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="80" yWindow="100" windowWidth="25440" windowHeight="13540" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
   <si>
     <t>Debt is formed from finance and operating leases</t>
   </si>
@@ -107,13 +107,16 @@
   </si>
   <si>
     <t>This share number is ound in the 10-K/10-Q in the EPS calculation table in the denominator part: dilutive potential common shares</t>
+  </si>
+  <si>
+    <t>In case you want to include operating leases as debt</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -133,6 +136,13 @@
       <color theme="1"/>
       <name val="Helvetica"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -167,13 +177,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -556,7 +567,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825B172E-7ADE-4B4A-B533-F037BCFCDCB0}">
-  <dimension ref="A2:G22"/>
+  <dimension ref="A2:G23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="1"/>
@@ -576,97 +587,102 @@
       <c r="G2" s="3"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="1" t="s">
-        <v>0</v>
+      <c r="B4" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B7" s="1" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B9" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B12" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B13" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B14" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B17" s="2" t="s">
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B18" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="3" t="s">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B21" s="1" t="s">
-        <v>21</v>
-      </c>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B22" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B23" s="1" t="s">
         <v>22</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A20:G20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/9. Statement and Data Notes.xlsx
+++ b/9. Statement and Data Notes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E69D214F-627C-2646-A4EE-B2266F272715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D74C6D1-7E48-234D-8CFF-3DFD59B0CC91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="80" yWindow="100" windowWidth="25440" windowHeight="13540" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
   <si>
     <t>Debt is formed from finance and operating leases</t>
   </si>
@@ -110,6 +110,9 @@
   </si>
   <si>
     <t>In case you want to include operating leases as debt</t>
+  </si>
+  <si>
+    <t>A proxy for cost of debt is to find the closest bonds with maturity 10 years from now and get the yield to maturity</t>
   </si>
 </sst>
 </file>
@@ -181,10 +184,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -567,7 +570,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825B172E-7ADE-4B4A-B533-F037BCFCDCB0}">
-  <dimension ref="A2:G23"/>
+  <dimension ref="A2:G27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="1"/>
@@ -576,18 +579,18 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>23</v>
       </c>
     </row>
@@ -642,15 +645,15 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
@@ -658,15 +661,15 @@
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B22" s="1" t="s">
@@ -678,11 +681,28 @@
         <v>22</v>
       </c>
     </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B27" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A16:G16"/>
     <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A25:G25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -698,15 +718,15 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
@@ -714,15 +734,15 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
@@ -730,15 +750,15 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B12" s="1" t="s">
@@ -765,15 +785,15 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
